--- a/output/BRI_Forensic_Transaction_Analysis_5Bulan_2026.xlsx
+++ b/output/BRI_Forensic_Transaction_Analysis_5Bulan_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\amal\tracking-dosa-zahra\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB13092-696C-453F-A0E7-53F1944FB60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E704E4-C7F6-40C5-9CE1-1354CA0DEF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daftar Transaksi" sheetId="1" r:id="rId1"/>
@@ -2569,11 +2569,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="&quot;Rp&quot;\ #,##0"/>
-    <numFmt numFmtId="168" formatCode="&quot;Rp&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="&quot;Rp&quot;\ #,##0"/>
+    <numFmt numFmtId="166" formatCode="&quot;Rp&quot;#,##0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2586,6 +2586,20 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2628,7 +2642,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2639,13 +2653,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2654,13 +2668,16 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="42" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2672,6 +2689,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3007,92 +3028,92 @@
     <col min="29" max="29" width="63.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:29" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="16" t="s">
         <v>28</v>
       </c>
     </row>
@@ -17590,7 +17611,7 @@
       <c r="A5" s="3" t="s">
         <v>782</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="9">
         <v>73344644</v>
       </c>
     </row>
@@ -17598,7 +17619,7 @@
       <c r="A6" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="9">
         <v>42528698</v>
       </c>
     </row>
@@ -17606,7 +17627,7 @@
       <c r="A7" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="9">
         <v>81682563</v>
       </c>
     </row>
@@ -17614,7 +17635,7 @@
       <c r="A8" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="9">
         <v>50866617</v>
       </c>
     </row>
@@ -23040,7 +23061,7 @@
     <col min="2" max="2" width="19.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.1796875" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" style="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.6328125" bestFit="1" customWidth="1"/>
@@ -23059,7 +23080,7 @@
       <c r="D1" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>783</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -23085,7 +23106,7 @@
       <c r="D2" s="6">
         <v>15144374</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="14">
         <v>10005984</v>
       </c>
       <c r="F2" s="6">
@@ -23111,7 +23132,7 @@
       <c r="D3" s="6">
         <v>9098512</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="14">
         <v>10006130</v>
       </c>
       <c r="F3" s="6">
@@ -23137,7 +23158,7 @@
       <c r="D4" s="6">
         <v>16491129</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="14">
         <v>11005791</v>
       </c>
       <c r="F4" s="6">
@@ -23163,7 +23184,7 @@
       <c r="D5" s="6">
         <v>19317828</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="14">
         <v>11505641</v>
       </c>
       <c r="F5" s="6">
@@ -23189,7 +23210,7 @@
       <c r="D6" s="6">
         <v>13292801</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="14">
         <v>5152</v>
       </c>
       <c r="F6" s="6">
@@ -23356,16 +23377,16 @@
         <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>67</v>
+        <v>450</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>67</v>
+        <v>451</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
@@ -25448,7 +25469,7 @@
     <col min="3" max="3" width="28.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -25468,7 +25489,7 @@
       <c r="E1" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>783</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -25491,7 +25512,7 @@
       <c r="E2" s="6">
         <v>25400000</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="11">
         <v>0</v>
       </c>
       <c r="G2" s="8">
@@ -25514,7 +25535,7 @@
       <c r="E3" s="6">
         <v>20628000</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="11">
         <v>0</v>
       </c>
       <c r="G3" s="8">
@@ -25537,7 +25558,7 @@
       <c r="E4" s="6">
         <v>0</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="11">
         <v>1000000</v>
       </c>
       <c r="G4" s="8">
@@ -25560,7 +25581,7 @@
       <c r="E5" s="6">
         <v>3302934</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="11">
         <v>0</v>
       </c>
       <c r="G5" s="8">
@@ -25583,7 +25604,7 @@
       <c r="E6" s="6">
         <v>1320200</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="11">
         <v>0</v>
       </c>
       <c r="G6" s="8">
@@ -25606,7 +25627,7 @@
       <c r="E7" s="6">
         <v>3637071</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="11">
         <v>0</v>
       </c>
       <c r="G7" s="8">
@@ -25629,7 +25650,7 @@
       <c r="E8" s="6">
         <v>0</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="11">
         <v>28698</v>
       </c>
       <c r="G8" s="8">
@@ -25652,7 +25673,7 @@
       <c r="E9" s="6">
         <v>5739</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="11">
         <v>0</v>
       </c>
       <c r="G9" s="8">
@@ -25675,7 +25696,7 @@
       <c r="E10" s="6">
         <v>34000</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="11">
         <v>0</v>
       </c>
       <c r="G10" s="8">
@@ -25698,7 +25719,7 @@
       <c r="E11" s="6">
         <v>17500</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="11">
         <v>0</v>
       </c>
       <c r="G11" s="8">
@@ -25721,7 +25742,7 @@
       <c r="E12" s="6">
         <v>0</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="11">
         <v>41500000</v>
       </c>
       <c r="G12" s="8">
@@ -25744,7 +25765,7 @@
       <c r="E13" s="6">
         <v>4500000</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="11">
         <v>0</v>
       </c>
       <c r="G13" s="8">
@@ -25767,7 +25788,7 @@
       <c r="E14" s="6">
         <v>14499200</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="11">
         <v>0</v>
       </c>
       <c r="G14" s="8">
